--- a/artfynd/A 8985-2022 artfynd.xlsx
+++ b/artfynd/A 8985-2022 artfynd.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Hedin, Mattias Larsson</t>
+          <t>Mattias Larsson, Jan Hedin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8985-2022 artfynd.xlsx
+++ b/artfynd/A 8985-2022 artfynd.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Larsson, Jan Hedin</t>
+          <t>Jan Hedin, Mattias Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 8985-2022 artfynd.xlsx
+++ b/artfynd/A 8985-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124708259</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
